--- a/data/trans_orig/IP07A14-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07A14-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2007 (tasa de respuesta: 99,5%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el adulto en 2007 (tasa de respuesta: 99,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36738</t>
+          <t>36711</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48763</t>
+          <t>48683</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>49606</t>
+          <t>49234</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>63159</t>
+          <t>63355</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>89681</t>
+          <t>89945</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107775</t>
+          <t>108031</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>74,59%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13833</t>
+          <t>14340</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25919</t>
+          <t>25985</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15040</t>
+          <t>15058</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28054</t>
+          <t>28351</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32988</t>
+          <t>33122</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50470</t>
+          <t>50183</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,65%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6460</t>
+          <t>6545</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8912</t>
+          <t>8430</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53028</t>
+          <t>52584</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68852</t>
+          <t>68409</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52842</t>
+          <t>52898</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>67300</t>
+          <t>67249</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,25%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>110803</t>
+          <t>109530</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131546</t>
+          <t>131401</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,66%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32987</t>
+          <t>33411</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48537</t>
+          <t>49176</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27556</t>
+          <t>28156</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41836</t>
+          <t>42814</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>64692</t>
+          <t>64382</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>85625</t>
+          <t>86425</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,53%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>638</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>5823</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8149</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3120</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11225</t>
+          <t>10219</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>4276</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3714</t>
+          <t>3057</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30885</t>
+          <t>31650</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42517</t>
+          <t>43479</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38222</t>
+          <t>38966</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49836</t>
+          <t>50175</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>73136</t>
+          <t>73031</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89930</t>
+          <t>90247</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,43%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,86%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15921</t>
+          <t>14939</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26939</t>
+          <t>26203</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14646</t>
+          <t>13898</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25573</t>
+          <t>24937</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32808</t>
+          <t>32496</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48709</t>
+          <t>48680</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,23%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5900</t>
+          <t>6342</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5654</t>
+          <t>5903</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2413</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9509</t>
+          <t>9715</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38743</t>
+          <t>38348</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55343</t>
+          <t>54525</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45081</t>
+          <t>44254</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60772</t>
+          <t>60395</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>88579</t>
+          <t>87731</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>111248</t>
+          <t>111236</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,43%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30523</t>
+          <t>31265</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46515</t>
+          <t>47740</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34802</t>
+          <t>34576</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>50828</t>
+          <t>50186</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>68862</t>
+          <t>69288</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>91648</t>
+          <t>90979</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>47,79%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9739</t>
+          <t>9665</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>1387</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8393</t>
+          <t>8519</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5105</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>15363</t>
+          <t>15432</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>173881</t>
+          <t>174321</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>202363</t>
+          <t>202776</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>200880</t>
+          <t>200621</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>229271</t>
+          <t>229733</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>382105</t>
+          <t>383336</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>422273</t>
+          <t>424445</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,75%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>104517</t>
+          <t>105433</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>133432</t>
+          <t>133922</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>104025</t>
+          <t>103871</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>131365</t>
+          <t>132051</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>217383</t>
+          <t>216791</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>257534</t>
+          <t>258134</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,77%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>6780</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18643</t>
+          <t>18268</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>8009</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>19634</t>
+          <t>19234</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>17706</t>
+          <t>17449</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>32249</t>
+          <t>32646</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3195</t>
+          <t>4154</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3961</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3545</t>
+          <t>3305</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3317</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2012 (tasa de respuesta: 97,81%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el adulto en 2012 (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36963</t>
+          <t>37079</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49665</t>
+          <t>49563</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,45%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41329</t>
+          <t>41285</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>54640</t>
+          <t>54810</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80956</t>
+          <t>82354</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100141</t>
+          <t>100711</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>73,18%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15300</t>
+          <t>15402</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28002</t>
+          <t>27886</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15723</t>
+          <t>15712</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29098</t>
+          <t>28442</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35126</t>
+          <t>34812</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53489</t>
+          <t>52960</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6467</t>
+          <t>6635</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>828</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>7524</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57013</t>
+          <t>57065</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71928</t>
+          <t>71631</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>57,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53337</t>
+          <t>53801</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68851</t>
+          <t>68810</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>55,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>115201</t>
+          <t>116146</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>136655</t>
+          <t>136701</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,88%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25254</t>
+          <t>25494</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39979</t>
+          <t>40450</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25326</t>
+          <t>25442</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40101</t>
+          <t>39805</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>55226</t>
+          <t>54637</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>76234</t>
+          <t>74476</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,07%</t>
         </is>
       </c>
     </row>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>3826</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7288</t>
+          <t>7257</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8918</t>
+          <t>8854</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32319</t>
+          <t>31955</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45294</t>
+          <t>44354</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,58%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47602</t>
+          <t>46846</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>57901</t>
+          <t>57850</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83827</t>
+          <t>82856</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>100178</t>
+          <t>100206</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>73,65%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19214</t>
+          <t>19576</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32065</t>
+          <t>31424</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9642</t>
+          <t>10049</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19909</t>
+          <t>20619</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31684</t>
+          <t>31809</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47251</t>
+          <t>48227</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>35,45%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>516</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5262</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>427</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>4306</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6912</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2960</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3485</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3342</t>
+          <t>3367</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>3590</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6280,7 +6280,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40600</t>
+          <t>41432</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57142</t>
+          <t>57931</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45901</t>
+          <t>46106</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62536</t>
+          <t>61714</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>93134</t>
+          <t>92699</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>115712</t>
+          <t>116353</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,58%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29819</t>
+          <t>28983</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46440</t>
+          <t>44817</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>23403</t>
+          <t>23526</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>38765</t>
+          <t>38940</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>58019</t>
+          <t>56712</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>79316</t>
+          <t>79750</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,58%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1587</t>
+          <t>1525</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9845</t>
+          <t>9435</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2309</t>
+          <t>2372</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10250</t>
+          <t>10786</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>5214</t>
+          <t>5440</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16625</t>
+          <t>16407</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -6799,7 +6799,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>3472</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6834,7 +6834,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>182340</t>
+          <t>180646</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>210974</t>
+          <t>210346</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>204120</t>
+          <t>203541</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>231921</t>
+          <t>229957</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>392738</t>
+          <t>394004</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>432944</t>
+          <t>434928</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,67%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>102400</t>
+          <t>102923</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>130750</t>
+          <t>131685</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>85080</t>
+          <t>88574</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>112838</t>
+          <t>113729</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>197831</t>
+          <t>195150</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>237598</t>
+          <t>236079</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,19%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>3709</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13115</t>
+          <t>12874</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8006</t>
+          <t>7877</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>19400</t>
+          <t>19324</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>13394</t>
+          <t>13973</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>28033</t>
+          <t>29077</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4643</t>
+          <t>4169</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3389</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de sentirse feliz en casa en 2016 (tasa de respuesta: 98,72%)</t>
+          <t>Menores según la frecuencia de sentirse feliz en casa, percibida por el adulto en 2016 (tasa de respuesta: 98,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38796</t>
+          <t>38289</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51597</t>
+          <t>51765</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44035</t>
+          <t>43514</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57981</t>
+          <t>58065</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>87503</t>
+          <t>86914</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106632</t>
+          <t>106834</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,95%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17103</t>
+          <t>17128</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29966</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13626</t>
+          <t>13707</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26583</t>
+          <t>27598</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>33348</t>
+          <t>32623</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51979</t>
+          <t>51634</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>35,74%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>593</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>717</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6293</t>
+          <t>6211</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1819</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57207</t>
+          <t>57814</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73606</t>
+          <t>74179</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61966</t>
+          <t>62391</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77621</t>
+          <t>78086</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>124484</t>
+          <t>125783</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>147900</t>
+          <t>147498</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>69,07%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25936</t>
+          <t>26107</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41110</t>
+          <t>41294</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25031</t>
+          <t>25218</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40494</t>
+          <t>40177</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>55169</t>
+          <t>55562</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>77679</t>
+          <t>76220</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>35,69%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11188</t>
+          <t>10677</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1354</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7936</t>
+          <t>8057</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6109</t>
+          <t>5892</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15664</t>
+          <t>15739</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>5377</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9170,7 +9170,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41631</t>
+          <t>41853</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54770</t>
+          <t>54189</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46500</t>
+          <t>46801</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60363</t>
+          <t>60360</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>93330</t>
+          <t>93193</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>112329</t>
+          <t>111594</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>74,95%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14598</t>
+          <t>15183</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27665</t>
+          <t>27012</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14390</t>
+          <t>13915</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27476</t>
+          <t>27002</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31609</t>
+          <t>32325</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50270</t>
+          <t>50117</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,66%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>646</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6058</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9626,7 +9626,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>758</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>7879</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>2450</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10620</t>
+          <t>10149</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57812</t>
+          <t>57219</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>74874</t>
+          <t>74692</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>55771</t>
+          <t>55111</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>72259</t>
+          <t>72418</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>120307</t>
+          <t>119522</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>143331</t>
+          <t>142596</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,22%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>29625</t>
+          <t>29368</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47369</t>
+          <t>47341</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27737</t>
+          <t>27914</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>44273</t>
+          <t>44540</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>61439</t>
+          <t>61201</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>84528</t>
+          <t>84218</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,29%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7181</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10328,7 +10328,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4601</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>9815</t>
+          <t>9790</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>212762</t>
+          <t>212785</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>242260</t>
+          <t>241958</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>225622</t>
+          <t>226462</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>253489</t>
+          <t>254945</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>445240</t>
+          <t>443888</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>488932</t>
+          <t>485465</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>67,81%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>101117</t>
+          <t>99988</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>130493</t>
+          <t>128408</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>95367</t>
+          <t>94434</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>122534</t>
+          <t>121460</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>201472</t>
+          <t>204383</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>242365</t>
+          <t>243942</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,07%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8857</t>
+          <t>9293</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>20773</t>
+          <t>21931</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,82 +10985,82 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>6,15%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>10760</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>6362</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>16910</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>4,71%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>25157</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>17768</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>34209</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>3,51%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
           <t>2,48%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>10760</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>6278</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>16957</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>25157</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>18560</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>35355</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5961</t>
+          <t>4629</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
